--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -723,60 +731,64 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +802,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>3/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +850,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +860,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,43 +921,951 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>07:10</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>—/3</t>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -999,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -1108,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,33 +1169,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1413,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1528,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1639,7 +1655,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1750,7 +1766,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1758,22 +1774,22 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1806,12 +1822,12 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1860,12 +1876,805 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1118,19 +1118,19 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,37 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1572,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1605,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1683,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1716,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1794,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1827,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1851,37 +1875,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1909,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1942,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1966,37 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2111,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2222,7 +2250,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2332,12 +2360,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2448,7 +2476,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2559,7 +2587,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2669,12 +2697,920 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1824,12 +1824,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1943,24 +1943,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2167,32 +2167,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2224,33 +2228,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2278,32 +2286,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2311,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2335,17 +2347,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2355,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2393,32 +2405,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -2426,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2450,33 +2466,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2504,32 +2524,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2537,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,33 +2585,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2615,32 +2643,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2648,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2672,37 +2704,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2730,32 +2762,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2763,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2787,33 +2823,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2881,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2874,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2898,33 +2942,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3150,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3250,7 +3298,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3265,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3375,12 +3423,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3495,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3503,22 +3551,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3551,12 +3599,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3570,47 +3618,967 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,18 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1542,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2013,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2615,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2918,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2976,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3000,32 +3004,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3033,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3057,33 +3065,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3111,32 +3123,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3144,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,17 +3184,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3188,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3226,32 +3242,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3259,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,17 +3303,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3303,12 +3323,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3341,32 +3361,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3374,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,32 +3422,32 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3456,32 +3480,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -3489,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,37 +3541,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3571,32 +3599,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3604,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3628,17 +3660,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3648,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3686,32 +3718,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3719,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3743,37 +3779,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3801,32 +3837,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -3834,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3858,37 +3898,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3916,32 +3956,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -3949,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3973,37 +4017,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4118,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4218,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4233,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4348,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4453,12 +4497,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4524,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4582,6 +4626,811 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,22 +2842,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3799,17 +3799,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3847,24 +3847,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3966,24 +3966,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4075,32 +4075,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4108,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4132,17 +4136,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4152,17 +4156,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4190,32 +4194,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4223,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,17 +4255,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4267,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4305,32 +4313,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4338,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4362,37 +4374,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4535,32 +4547,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4568,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4592,37 +4608,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4650,32 +4666,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4683,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4707,17 +4727,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4727,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4765,32 +4785,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4798,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4822,37 +4846,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4880,32 +4904,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4913,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,17 +4965,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4957,17 +4985,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5077,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5182,7 +5210,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5197,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5422,12 +5450,698 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,14 +1656,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2018,17 +2018,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,14 +3199,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>77.0</t>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,17 +3913,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,12 +4037,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4914,24 +4914,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5023,32 +5023,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -5056,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5080,17 +5084,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5100,12 +5104,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5138,32 +5142,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5171,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5203,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5253,32 +5261,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5286,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5310,17 +5322,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5330,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5368,32 +5380,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -5401,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5425,32 +5441,32 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5483,32 +5499,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5516,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,17 +5560,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5560,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5598,32 +5618,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5631,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,37 +5679,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5800,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5900,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5972,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,17 +6040,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6145,6 +6169,577 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,14 +2013,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,14 +3437,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,14 +5218,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5390,24 +5390,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,17 +5461,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5509,24 +5509,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5628,24 +5628,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5737,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5794,37 +5798,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5852,32 +5856,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -5885,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,17 +5917,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5929,13 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5963,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5996,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,29 +6036,29 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -6050,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6078,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6111,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,37 +6155,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6193,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -6226,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,17 +6274,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6270,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6380,7 +6404,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6395,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6437,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6456,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6470,7 +6494,7 @@
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
@@ -6505,12 +6529,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6633,22 +6657,22 @@
       <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6681,12 +6705,12 @@
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6725,18 +6749,597 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5997,12 +5997,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,14 +2604,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,17 +3199,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,22 +3556,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,22 +3913,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,14 +4270,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,17 +4394,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,22 +5456,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6104,24 +6104,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6223,24 +6223,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6332,32 +6332,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6365,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6389,17 +6393,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6409,12 +6413,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6447,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6480,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6504,17 +6512,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6524,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6562,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6595,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6619,32 +6631,32 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6677,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6710,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,37 +6750,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6792,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -6825,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,17 +6869,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6869,7 +6889,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6879,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6994,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7104,12 +7124,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7232,22 +7252,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7280,12 +7300,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7299,47 +7319,737 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>82.5</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,14 +1894,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,22 +2013,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,22 +3437,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,14 +3794,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,14 +4980,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,22 +5218,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6699,24 +6699,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6818,24 +6818,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6927,32 +6927,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6960,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6984,32 +6988,32 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7042,32 +7046,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7075,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7099,17 +7107,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7119,17 +7127,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7157,32 +7165,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7190,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7214,37 +7226,37 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7272,32 +7284,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -7305,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7329,32 +7345,32 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7387,32 +7403,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7420,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7444,17 +7464,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7464,12 +7484,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7535,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7574,7 +7594,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7597,22 +7617,22 @@
       <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -7645,12 +7665,12 @@
       <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7689,22 +7709,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7712,22 +7732,22 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7760,12 +7780,12 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7779,7 +7799,7 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
@@ -7804,17 +7824,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7880,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7995,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8044,12 +8064,1047 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>77.5</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>77.5</t>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3080,22 +3080,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,22 +3199,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,14 +3913,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,14 +5456,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,22 +5694,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,22 +5813,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,14 +6170,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>77.5</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,14 +6289,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,22 +6646,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7003,22 +7003,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,14 +7122,14 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>77.5</t>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7294,24 +7294,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7425,12 +7425,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7522,32 +7522,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7555,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7583,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7599,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7637,32 +7641,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -7670,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,29 +7702,29 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -7724,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7752,32 +7760,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7785,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7809,37 +7821,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7939,7 +7951,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8015,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,7 +8066,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8069,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8097,32 +8109,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -8130,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8154,37 +8170,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8284,7 +8300,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8327,32 +8343,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8360,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8384,37 +8404,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8590,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8644,7 +8664,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8759,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8935,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8984,12 +9004,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8997,22 +9017,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9045,12 +9065,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9064,47 +9084,1082 @@
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr">
         <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>11/15</t>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,22 +1894,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,17 +3675,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,22 +3794,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,22 +3913,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,22 +5456,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,17 +6170,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,17 +6408,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,17 +7122,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,17 +7360,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7479,17 +7479,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7717,22 +7717,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7994,32 +7994,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -8027,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8055,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8071,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8261,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8353,24 +8357,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8380,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8429,12 +8433,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8462,32 +8466,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -8495,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,37 +8527,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8577,32 +8585,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8610,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8634,37 +8646,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8764,7 +8776,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8840,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8879,7 +8891,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8922,32 +8934,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -8955,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8979,32 +8995,32 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9037,32 +9053,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9070,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9094,32 +9114,32 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9185,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9224,7 +9244,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9267,32 +9287,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9300,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9324,32 +9348,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9382,32 +9406,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -9415,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9439,37 +9467,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9530,7 +9558,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9569,7 +9597,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9645,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9760,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9875,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9990,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10034,17 +10062,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10052,22 +10080,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10100,12 +10128,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10119,47 +10147,1197 @@
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="W83" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z83" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA83" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>12/15</t>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,17 +1537,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3318,17 +3318,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4032,22 +4032,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4389,22 +4389,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,17 +4504,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,22 +5694,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,22 +6527,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7360,22 +7360,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7951,17 +7951,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8189,22 +8189,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8309,17 +8309,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8547,7 +8547,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8891,17 +8891,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9010,22 +9010,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9297,19 +9297,19 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9416,24 +9416,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9525,32 +9525,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9558,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9582,17 +9586,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9602,12 +9606,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9640,32 +9644,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9673,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9697,32 +9705,32 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9755,32 +9763,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9788,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9812,37 +9824,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9870,32 +9882,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9903,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9927,17 +9943,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9947,17 +9963,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10057,7 +10073,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10100,32 +10116,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -10133,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10157,17 +10177,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10177,7 +10197,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10215,32 +10235,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10248,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10272,17 +10296,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10292,12 +10316,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10363,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10402,7 +10426,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10417,7 +10441,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10445,32 +10469,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10478,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10502,32 +10530,32 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10593,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10647,7 +10675,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10675,32 +10703,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10708,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10732,37 +10764,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10823,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10938,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10977,7 +11009,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11053,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11102,12 +11134,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11217,7 +11249,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11283,7 +11315,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11327,17 +11359,822 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB92" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>7/15</t>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3204,17 +3204,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7127,17 +7127,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9134,17 +9134,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9368,17 +9368,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,17 +9606,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9844,12 +9844,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10822,32 +10822,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10855,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10879,17 +10883,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10899,17 +10903,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10937,32 +10941,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -10970,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10994,17 +11002,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11014,12 +11022,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11052,32 +11060,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11085,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11109,17 +11121,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11129,17 +11141,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -11167,32 +11179,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -11200,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11224,17 +11240,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11244,12 +11260,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11282,32 +11298,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11315,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11339,17 +11359,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11359,17 +11379,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11397,32 +11417,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11430,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11454,17 +11478,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11474,12 +11498,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11545,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11660,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11775,7 +11799,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11890,7 +11914,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11952,22 +11976,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -12000,12 +12024,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12019,7 +12043,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12049,17 +12073,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -12067,22 +12091,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12115,12 +12139,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12134,47 +12158,507 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>79.8</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>10/15</t>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7613,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10078,17 +10078,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11032,7 +11032,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11536,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11569,7 +11573,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11593,17 +11597,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11613,12 +11617,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11766,32 +11770,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11799,7 +11807,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11823,17 +11831,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11843,17 +11851,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11996,32 +12004,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -12029,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12053,17 +12065,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12073,12 +12085,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12144,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12226,32 +12238,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -12259,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12283,17 +12299,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12303,7 +12319,7 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
@@ -12374,7 +12390,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12428,7 +12444,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12505,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12533,12 +12549,12 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12604,7 +12620,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">

--- a/data/export/2026-09-27-浦东78路.xlsx
+++ b/data/export/2026-09-27-浦东78路.xlsx
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7603,17 +7603,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9249,17 +9249,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11022,17 +11022,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -12014,24 +12014,24 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12123,32 +12123,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -12156,7 +12160,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12180,17 +12184,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12200,12 +12204,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12248,24 +12252,24 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12275,7 +12279,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12324,7 +12328,7 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12357,32 +12361,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -12390,7 +12398,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12414,17 +12422,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12434,17 +12442,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12513,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12554,7 +12562,7 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12620,7 +12628,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12664,12 +12672,12 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
